--- a/papers/P001-za-sam/outputs/P001_SA_SAM_2019_v02.xlsx
+++ b/papers/P001-za-sam/outputs/P001_SA_SAM_2019_v02.xlsx
@@ -447,7 +447,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-16 by papers/P001-za-sam/code/12_generate_workbook.py.</t>
+          <t>Generated by papers/P001-za-sam/code/12_generate_workbook.py.</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -726,6 +726,54 @@
           <t>07be2dfea79f3431e16548c398dcd96f83444fc8862c44a2d6ede5f3586b792a</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S-008 — IFPRI 2019 Nexus SAM for Kenya — OBTAINED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>a949a1e6…b08cc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S-009 — KNBS 2009 SUT — OBTAINED (CONDENSED); DETAILED VERSION HELD BY KNBS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>e12fe005…b394</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S-010 — KNBS Economic Survey 2020 + 2019 — OBTAINED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>aa52bbb8…873a8a2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S-011 — Eurostat NL 2019: supply-use tables and sector accounts — OBTAINED</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
